--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -526,6 +526,33 @@
         <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/17</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -553,6 +553,33 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/18</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -580,6 +580,33 @@
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/19</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -77,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -87,6 +87,9 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -453,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -610,6 +613,33 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -621,15 +651,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
     <col width="8.4" customWidth="1" min="2" max="2"/>
-    <col width="8.4" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8.4" customWidth="1" min="5" max="5"/>
-    <col width="7.5" customWidth="1" min="6" max="6"/>
+    <col width="11.1" customWidth="1" min="3" max="3"/>
+    <col width="20.55" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="16.05" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -661,6 +691,38 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>링크 URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>광주매일신문</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>[지면 12면] 광주경제진흥상생일자리재단 은19일“최근지역뷰티기업의온라인판로확대와디지털경쟁력강화</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>https://kjdaily.wigoview.com/</t>
         </is>
       </c>
     </row>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -638,6 +638,33 @@
       </c>
       <c r="G6" s="3" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/21</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -664,6 +664,33 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -691,6 +691,33 @@
         <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/23</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -718,6 +718,33 @@
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/24</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -745,6 +745,33 @@
         <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/25</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -772,6 +772,33 @@
         <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -799,6 +799,33 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -829,6 +829,114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/28</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/28</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/28</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/28</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -840,15 +948,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
     <col width="8.4" customWidth="1" min="2" max="2"/>
-    <col width="11.1" customWidth="1" min="3" max="3"/>
+    <col width="13.35" customWidth="1" min="3" max="3"/>
     <col width="20.55" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="16.05" customWidth="1" min="6" max="6"/>
+    <col width="41.25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -915,6 +1023,102 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/28</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/28</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>폭염 속 밭일 외국인노동자 숨져…안전 수칙 ‘사각지대’</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>https://news.kbs.co.kr/news/view.do?ncd=8621831&amp;amp;ref=DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/28</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/28</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>남도일보</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>[지면 15면] 입되는외국인노동자가많은점을고</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.namdonews.com/pdf/php/check.php?category=&amp;y=2026&amp;m=07&amp;d=28&amp;page=15&amp;hosu=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/28</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/28</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>“교단 성폭력 대응 조사 5년 결실… 연합기관만 할 수 있어”</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kmib.co.kr/article/view.asp?arcid=1785136001&amp;code=23111117</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -937,6 +937,114 @@
         <v>1</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/29</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/29</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/29</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/29</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -948,7 +1056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -1119,6 +1227,70 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/29</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/29</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>양산외국인근로자지원센터, 사업주 간담회</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.idomin.com/news/articleView.html?idxno=2011213</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/29</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/29</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>한강밤핑-디제잉… ‘야간 경제’ 더 키운다</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/Society/article/all/20260728/134382925/2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -1045,6 +1045,114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1056,7 +1164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -1291,6 +1399,70 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>[포토뉴스]원주 명륜종합사회복지관 청소년방과후아카데미 여름나기 힐링캠프·직업체험</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kwnews.co.kr/article/20260729500641</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>함평군, ‘마음휴가 힐링캠프’ 운영…군민 마음건강 돌본다</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>https://sports.donga.com/news/article/all/20260730/134391693/1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -1153,6 +1153,114 @@
         <v>2</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1164,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -1463,6 +1571,38 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>전남광주특별시, 대학생 소셜벤처 아이디어 공모전 참가자 모집</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>http://www.gwangnam.co.kr/article.php?aid=1785458000543597004</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -1261,6 +1261,114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/01</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/01</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/01</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/01</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1272,7 +1380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -1603,6 +1711,102 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/01</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/01</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>"지역사회 현안해결 대학생 아이디어 찾아요"</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.jnilbo.com/news/articleView.html?idxno=90000053741</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/01</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/01</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>정부, 반도체 메가특구 ‘주52시간 예외-기간제 2+2년’ 추진</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/Economy/article/all/20260731/134404450/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/01</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/01</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>호남 반도체 메가특구 ‘52시간’ 예외 추진…기간제도 4년까지</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/Economy/article/all/20260731/134401444/1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -1366,6 +1366,114 @@
         <v>0</v>
       </c>
       <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/02</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/02</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/02</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/02</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -1477,6 +1477,114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1488,7 +1596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -1915,6 +2023,358 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>경기도 온열질환 사망자 2명으로 늘어…추가 조사 중</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>http://www.obsnews.co.kr/news/articleView.html?idxno=1532719</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>연일 '가마솥 폭염'에 도심 피서지는 '인산인해'</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kihoilbo.co.kr/news/articleView.html?idxno=3030554</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>SM C&amp;C 엔터사업부문 최영인 신임 대표 선임</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>https://view.asiae.co.kr/article/2026080315072034534</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>SM C&amp;C 엔터사업부문 대표에 최영인 前 SBS 예능본부장</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.munhwa.com/article/11606884?ref=kpf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>SM C&amp;C 엔터부문 대표에 최영인</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.naeil.com/news/read/597502?ref=bigkinds</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>SM C&amp;C, 엔터사업부문 대표에 최영인 전 SBS 예능본부장 선임</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>http://www.fnnews.com/news/202608031017315027</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>SM C&amp;C, 엔터사업부문 신임 대표에 최영인 전 SBS 예능본부장 선임</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>https://biz.heraldcorp.com/article/10828787</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>SM C&amp;C 엔터사업 신임 대표에 최영인 전 SBS예능본부장</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.dt.co.kr/article/12076166?ref=jeadan</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>최영인 전 SBS 예능본부장, SM C&amp;C 엔터사업 대표 선임</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>http://www.mk.co.kr/article/12114881</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>SM C&amp;C 엔터사업부문 대표에 최영인 전 SBS 예능본부장</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>https://view.asiae.co.kr/article/2026080309114371584</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>최영인, SM C&amp;C 엔터사업부문 대표 선임…디지털 스튜디오 이끈다</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>https://sports.donga.com/news/article/all/20260803/134410511/1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -1585,6 +1585,114 @@
         <v>10</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/04</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/04</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/04</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/04</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1596,7 +1704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -2375,6 +2483,166 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/04</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/04</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>사천시, 외국인노동자 정착지원 복합센터 건립 본격화</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.idomin.com/news/articleView.html?idxno=2011647</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/04</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/04</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>김해분청도자박물관 개관 17주년, 외국인노동자 도자 작품 특별전</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.idomin.com/news/articleView.html?idxno=2011637</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/04</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/04</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>이주노동자 110만 시대…인권침해 '원스톱 긴급구제' 절실</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bigkinds.or.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/04</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/04</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>SM C＆C, 최영인 엔터사업부문 대표 선임</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.seoul.co.kr/news/newsView.php?id=20260804023004</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/04</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/04</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>서울 곳곳이 여름방학 ‘문화 피서지’</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/Society/article/all/20260803/134395787/2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -1693,6 +1693,114 @@
         <v>2</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1704,7 +1812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -2643,6 +2751,166 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>'표 계산'에 외면받는 인권… 외국인 노동자엔 없는 '법적 울타리'</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bigkinds.or.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>‘청년 조용기’에 네 번 울었어요… “영웅 아닌 하나님 보여주는 영화”</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kmib.co.kr/article/view.asp?arcid=1785747579&amp;code=23111513</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>"외국인노동자 부당해고 구제과정서 차별 당했다"</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksilbo.co.kr/news/articleView.html?idxno=1063836</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>공주시, 세대공감 희망나누기 '1박 2일 우리가족 힐링캠프' 운영</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.daejonilbo.com/news/articleView.html?idxno=2292720</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>경남경총, 구직 포기 청년 재도전 돕는다</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bigkinds.or.kr/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -1801,6 +1801,114 @@
         <v>2</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1812,7 +1920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -2911,6 +3019,230 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>폭염에 가축 69만마리 폐사…송미령 "피해 예방에 가용자원 총동원"</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>https://view.asiae.co.kr/article/2026080614402904242</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>농작업 온열질환 사망 5명, 가축폐사 68만마리…농식품부 “가용자원 총동원 폭염 대응”</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.busan.com/view/busan/view.php?code=2026080614220803019</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>폭염에 가축 69만마리 폐사…논밭·하우스서 5명 숨지고 남부 50곳 가뭄</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.etoday.co.kr/news/view/2611716</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>농식품부, 폭염 대응 24시간 체제…농업인·외국인노동자 집중 관리</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bigkinds.or.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>야구 올스톱, 수문장 교대식-거리공연 취소… 폭염에 멈춘 일상</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/Society/article/all/20260805/134427802/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>폭염에 멈춘 대한민국…프로야구-야외 문화행사 줄줄이 중단</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/Society/article/all/20260805/134426090/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>“야” “인마” “어이” 이제 그만…이주노동자 호칭개선하자</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/Society/article/all/20260805/134426882/1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -1909,6 +1909,114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1920,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -3243,6 +3351,102 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단, 이동노동자 폭염 안전용품 지원</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bigkinds.or.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>폭염·가뭄 장기화…드론 예찰·긴급급수 총력 대응</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kihoilbo.co.kr/news/articleView.html?idxno=3031045</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>“순환장애 안면부종” 이지아, 성형설까지 났는데…곧 50세 깜짝 ‘미모’</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sportsseoul.com/news/read/1627164</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -2017,6 +2017,114 @@
         <v>1</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/08</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/08</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/08</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/08</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2028,7 +2136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -3447,6 +3555,38 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/08</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/08</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>걸음걸음마다 순례길… “잠시 멈추고 하나님을 만났다”</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kmib.co.kr/article/view.asp?arcid=9000001306&amp;code=23111112&amp;cp=kd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -2123,6 +2123,114 @@
       </c>
       <c r="G61" s="3" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/09</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/09</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/09</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/09</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -2233,6 +2233,114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2244,7 +2352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -3695,6 +3803,134 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단, 이동노동자에 폭염 안전용품 지원</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.jnilbo.com/news/articleView.html?idxno=90000055596</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>"차고지가 신도시"·"나 반포산다"…'버스 하우스' 제안에 비난·조롱 밈 폭발</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>http://www.fnnews.com/news/202608091844035592</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>“한국 가면 3~5배 번다”…베트남 청년 해외취업에 자국 산업은 비상</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/Inter/article/all/20260810/134448904/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>여주서 밭일하던 30대 외국인 여성노동자 숨진 채 발견</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/Society/article/all/20260810/134449090/1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -2341,6 +2341,114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2352,7 +2460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -3931,6 +4039,294 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>광주경제일자리재단, 지역 소상공인 프랜차이즈화 본격 지원</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.jnilbo.com/news/articleView.html?idxno=90000055900</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>마약류 범죄로부터 외국인노동자 보호</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>https://www.naeil.com/news/read/598402?ref=bigkinds</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>제주 외국인노동자 4년새 85% 증가…3778명</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.segye.com/newsView/20260811510709</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>산업인력공단-인천공항세관, '외국인노동자 안전조처' 강화</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>http://www.metroseoul.co.kr/article/20260811500144</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>산업인력공단·인천공항세관, 외국인근로자 입국 때부터 ‘마약범죄 예방교육’</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>https://biz.heraldcorp.com/article/10836989</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>외국인노동자 입국 때 마약범죄 예방 강화…산업인력공단-관세청 맞손</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bigkinds.or.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>제주지역 E9 외국인노동자 3778명… 노동·인권실태 조사 나선다</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.seoul.co.kr/news/newsView.php?id=20260811500048</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>외국인 불법 라이더 급증에…위법한 ‘부당거래’ 택한 단속 당국</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/Society/article/all/20260811/134456364/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>영암군, 캄보디아 계절노동자 20명 배치…무화과 수확철 일손 보탠다</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>https://sports.donga.com/news/article/all/20260810/134449782/1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -2449,6 +2449,114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/12</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/12</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/12</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/12</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2460,7 +2568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -4327,6 +4435,70 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/12</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/12</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>산업현장 외국인 노동자 실태조사 실시</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bigkinds.or.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/12</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/12</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>외국인노동자 입국 순간부터 마약 막는다…인천공항세관·산업인력공단 맞손</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.viva100.com/article/20260811501046</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -2557,6 +2557,114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2568,7 +2676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -4499,6 +4607,38 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>“잘 가, 크레이지 아케이드”…25년 여정 오늘 마침표</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/Economy/article/all/20260813/134470104/1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -2665,6 +2665,114 @@
         <v>1</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2676,7 +2784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -4639,6 +4747,134 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>고용허가제 송출국에 카자흐스탄 추가</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>https://www.naeil.com/news/read/598837?ref=bigkinds</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>정부, 18번째 고용허가제 송출국으로 카자흐스탄 지정…2028년 도입</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ajunews.com/view/20260814104708034</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>카자흐스탄 고용허가제 2028년부터 도입…E-9 비자 18번째 송출국</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bigkinds.or.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>남도일보</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>[지면 16면] 진도교육청, 인성함양힐링캠프</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>https://www.namdonews.com/pdf/php/check.php?category=&amp;y=2026&amp;m=08&amp;d=14&amp;page=16&amp;hosu=0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -2773,6 +2773,114 @@
         <v>1</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/15</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/15</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/15</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/15</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2784,7 +2892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -4875,6 +4983,70 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/15</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/15</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>강릉 모 초등학교 배수로 공사하던 외국인노동자 심정지 이송</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kado.net/news/articleView.html?idxno=2066853</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/15</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/15</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>경북 의성서 캄보디아 국적 30대 노동자, 기계 끼임 사고로 숨져</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/Society/article/all/20260815/134482962/1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -2878,6 +2878,114 @@
         <v>0</v>
       </c>
       <c r="G89" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/16</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/16</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/16</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/16</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -2989,6 +2989,114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3000,7 +3108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -5155,6 +5263,38 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>함안군 '기업지원 에스오에스(SOS)' 본격 가동</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>https://www.idomin.com/news/articleView.html?idxno=2012494</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -3097,6 +3097,114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3108,7 +3216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -5295,6 +5403,38 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단, 2027년 연구과제 수요조사 실시</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>https://www.jnilbo.com/news/articleView.html?idxno=90000057443</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -3205,6 +3205,114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3216,7 +3324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -5435,6 +5543,38 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>국립횡성숲체원, 지역 청소년 숲 힐링캠프 진행</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kwnews.co.kr/article/20260818500412</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -3313,6 +3313,114 @@
         <v>1</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3324,7 +3432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -5575,6 +5683,134 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>사장 실수로 '불법체류' 위기…권익위 "재고용 허가해야"</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bigkinds.or.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>일도 집도 다 잃을라… 할 말을 잃다</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mt.co.kr/society/2026/08/20/2026081919584635293</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>제천 청소년들, 생활 속 아이디어를 정책으로 제안</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>http://www.cctimes.kr/news/articleView.html?idxno=922583</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>신한은행, ‘인천시 금고 20년’ 안정적 시스템 강점…수성전 돌입</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kyeonggi.com/article/20260819580361</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -3421,6 +3421,114 @@
         <v>2</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3432,7 +3540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -5811,6 +5919,134 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>넥슨게임즈, 영케어러 지원 '위드영 프로젝트' 2기... 1억원 기부</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>http://www.etnews.com/20260821000109</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>넥슨게임즈, 영케어러 지원에 1억원 기부</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bigkinds.or.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>[Game &amp; Now] 넥슨게임즈ESG, 영케어러 '미래'까지 지원한다</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ebn.co.kr/news/articleView.html?idxno=1721157</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>넥슨게임즈, 영케어러 지원 ‘위드영 프로젝트 2기’ 시작…1억원 기부</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>https://www.segye.com/newsView/20260821504628</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -3529,6 +3529,114 @@
         <v>4</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/22</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/22</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/22</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/22</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3540,7 +3648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -6047,6 +6155,38 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/22</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/22</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>넥슨게임즈, 영케어러 지원 사업 ‘위드영 프로젝트 2기’ 위해 1억원 기부</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>https://www.viva100.com/article/20260821500147</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -3637,6 +3637,114 @@
         <v>1</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/23</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/23</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/23</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/23</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3648,7 +3756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -6187,6 +6295,70 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/23</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/23</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>산청의 탈북 맏며느리… “산청이 왜 천국인지 아십니까”[북에서 온 이웃]</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/Politics/article/all/20260820/134512613/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/23</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/23</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>형제자매 생이별 막는다…서울시, 통합 아동보호체계 구축해 입양 지원</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mt.co.kr/policy/2026/08/23/2026082213081778341</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -3745,6 +3745,114 @@
         <v>1</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3756,7 +3864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -6359,6 +6467,70 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>창원외국인근로자지원센터 폭염 대응 물품 나눔</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>https://www.idomin.com/news/articleView.html?idxno=2012975</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>남도일보</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>[지면 6면] 하던외국인노동자20대B씨가11층</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>https://www.namdonews.com/pdf/php/check.php?category=&amp;y=2026&amp;m=08&amp;d=24&amp;page=6&amp;hosu=0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -3853,6 +3853,114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/25</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/25</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/25</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/25</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3864,7 +3972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -6531,6 +6639,102 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/25</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/25</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>학교부터 일터까지…지역 맞춤형 노동교육 9개 시·도 시범운영</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mt.co.kr/economy/2026/08/25/2026082509261888318</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/25</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/25</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>노동부, 지자체와 지역 주도 노동교육…내년 전국으로 확대</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ajunews.com/view/20260825083809843</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/25</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/25</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>[광화문에서/이유종]이주배경 초중고생 20만명… ‘글로벌 역량’ 갖춘 인재로</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/Opinion/article/all/20260824/134535904/2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -3961,6 +3961,114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/26</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/26</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/26</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/26</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3972,7 +4080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -6735,6 +6843,70 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/26</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/26</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>태안해양치유센터, 대한민국 대표 힐링 명소로 우뚝!</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ccdailynews.com/news/articleView.html?idxno=2436264</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/26</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/26</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>서해의 품에서, 몸과 마음을 재충전하는 태안해양치유센터, 대한민국 대표 힐링 성지로 우뚝!</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>https://www.daejonilbo.com/news/articleView.html?idxno=2296684</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -4069,6 +4069,114 @@
         <v>3</v>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4080,7 +4188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -6907,6 +7015,262 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>“외국인노동자 보호 지원 조례 전면 재검토”</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>https://news.kbs.co.kr/news/view.do?ncd=8648265&amp;amp;ref=DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>"체류자격 따라 배제 안돼"…시민사회, 외국인노동자 조례 재검토 촉구</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>https://www.namdonews.com/news/articleView.html?idxno=921492</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>전남광주노동단체, 외국인노동자 조례 재검토 촉구</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>http://www.gwangnam.co.kr/article.php?aid=1787816514545622023</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>"미등록 이주노동자 배제하는 통합은 불가능해"…시민사회, 전남광주 외국인노동자 조례 '비판'</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bigkinds.or.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>양산외국인근로자지원센터, 한방진료 서비스</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>https://www.idomin.com/news/articleView.html?idxno=2013328</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>GKL ‘노·리·터’가 찾아왔다…커피 한잔에 고충 상담</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>https://sports.donga.com/news/article/all/20260827/134556191/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>부산 공장서 20대 외국인 노동자 포장기계에 끼여 중태</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/Society/article/all/20260827/134553581/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>“정말 잘못했다” 장윤정 모친, 결국 눈물…‘투자 사기’ 징역 1년6개월 구형</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>http://www.mk.co.kr/article/12137657</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G137"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -4177,6 +4177,114 @@
         <v>1</v>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4188,7 +4296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -7271,6 +7379,102 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>전남광주통합특별시, 통합 후 첫 ‘일자리 박람회’ 연다</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>http://www.gwangnam.co.kr/article.php?aid=1787895389545713004</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>제값 못 받는 무밭에 제초제… 경영난 시달리던 농민 숨져</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kado.net/news/articleView.html?idxno=2069137</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>남도일보</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>[지면 6면] 외국인노동자보호및지원조례안비판기자회견</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>https://www.namdonews.com/pdf/php/check.php?category=&amp;y=2026&amp;m=08&amp;d=28&amp;page=6&amp;hosu=0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -4285,6 +4285,114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/29</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/29</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/29</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/29</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4296,7 +4404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -7475,6 +7583,38 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/29</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/29</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>전남광주특별시, 첫 ‘상생 일자리박람회’ 개최… 47개 기업·307명 현장 채용</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>http://www.breaknews.com/1232550</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -4393,6 +4393,114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4404,7 +4512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -7615,6 +7723,166 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>전남광주, 내달 2일 통합 이후 첫 ‘일자리박람회’</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>http://www.kjdaily.com/news_view.php?n=685491&amp;tmp=20260830&amp;s=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>전남광주시, 내달 2일 '일자리 박람회' 연다…앰코·한전KDN 등 공공기관·기업 47곳 참여</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>http://www.etnews.com/20260830000035</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>고용노동부 포항지청, 경주 ‘외국인 노동자’ 고용사업장 안전보건·주거환경 집중현장점검</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>http://www.hidomin.com/news/articleView.html?idxno=719144</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>[정부 주요 일정] 경제·사회부처 주간 일정 (8월 31일 ~ 9월 4일)</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>https://www.etoday.co.kr/news/view/2619604</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>KB국민은행, 청년 IT 인재 양성 프로그램 수료식</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>http://www.metroseoul.co.kr/article/20260830500087</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -4501,6 +4501,114 @@
         <v>1</v>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4512,7 +4620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -7883,6 +7991,294 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>전남광주, 중소기업에 저금리 융자 100억 추가 투입</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>https://www.namdonews.com/news/articleView.html?idxno=921759</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>전남광주시, 중소기업 구조고도화자금 100억 융자 지원</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>https://www.jnilbo.com/news/articleView.html?idxno=90000061080</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>광주특별시, 중기 구조고도화자금 100억 융자 지원</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>http://www.gwangnam.co.kr/article.php?aid=1788154078545827004</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>소상공인 대상 서울대 문정훈 교수 초청 특강, 조기 마감 '성황'</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>https://www.namdonews.com/news/articleView.html?idxno=921755</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>광주특별시, 중소기업 구조고도화자금 100억원 융자 추가 지원</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>https://www.fnnews.com/news/202608311426504891</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>광주경제일자리재단, 푸드트렌드 명사 특강 ‘성황’</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>http://www.gwangnam.co.kr/article.php?aid=1788141068545805015</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>TYM, 전국기능경기대회에 트랙터 15대 무상 지원</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/article/all/20260831/134576948/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>인산가 웰니스호텔 "대기업 임직원 복지 수요 잡는다"</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>https://www.fnnews.com/news/202608311415259329</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>곡성군, ‘구석구석 문화가 있는 날’ 9월 프로그램 풍성</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>https://sports.donga.com/news/article/all/20260831/134576895/1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G153"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -4609,6 +4609,114 @@
         <v>2</v>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4620,7 +4728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -8279,6 +8387,230 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>서울살이 정보 한곳에…서울시, 외국인포털 ‘마이서울+’</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>https://go.seoul.co.kr/news/newsView.php?id=20260901500284</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>[2027 예산안] 노동부 예산 3.4% 늘어난 38.9조원…청년 취업과 산재예방에 방점</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bigkinds.or.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>‘K자형 양극화’ 해소에 117조…지역·농어촌·취약계층 지원 늘린다 [2027년 예산안]</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202609016030i</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>서울시, 외국인포털 개편…'MY SEOUL+' 출범</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>https://www.newspim.com/news/view/20260901000484</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>세계밀리터리룩 페스티벌, 내달 9~10일 연천서 개최</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bigkinds.or.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>화순군 드림스타트, ‘가족 힐링캠프’ 운영</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>http://www.metroseoul.co.kr/article/20260901500248</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>김민호 “광고 찍는 줄 알았는데 12시간 용역…집에 걸어오며 울었다”</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>https://sports.donga.com/news/article/all/20260831/134579950/1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:G161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -4717,6 +4717,114 @@
         <v>3</v>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/02</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/02</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/02</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/02</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4728,7 +4836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -8611,6 +8719,166 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/02</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/02</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>서울 거주 외국인 생활정보 ‘한눈에’</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>https://www.segye.com/newsView/20260901521294</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/02</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/02</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>“평창 벗어나 서울 야경 품었다”…학교 밖 청소년 채운 1박 2일의 ‘문화 힐링’</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bigkinds.or.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/02</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/02</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>평창, 학교밖 청소년 까지 보듬었다. 서울여행 행복한 어울림[함영훈의 멋·맛·쉼]</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>https://biz.heraldcorp.com/article/10860234</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/02</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/02</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>평창군학교밖청소년지원센터, 꿈드림 청소년 '서울 문화·힐링 캠프' 성료</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>http://www.breaknews.com/1233469</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/02</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/02</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>평창 학교 밖 청소년 서울서 문화·힐링캠프…공연·체험으로 교류 넓혀</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kukinews.com/article/view/kuk202609020077</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G161"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -4825,6 +4825,114 @@
         <v>4</v>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4836,7 +4944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F126"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -8879,6 +8987,38 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>평창 학교밖 청소년 서울서 ‘문화·힐링캠프’</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kwnews.co.kr/article/20260902500507</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:G169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -4933,6 +4933,114 @@
         <v>1</v>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4944,7 +5052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -9019,6 +9127,70 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>강원랜드, 제복 근무자 가족 위한 '영웅쉼터 2차 힐링캠프' 마무리</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>https://weekly.hankooki.com/news/articleView.html?idxno=7182567</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>강원랜드 ‘영웅쉼터’ 2박3일…제복 영웅에게 휴가를</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>https://sports.donga.com/news/article/all/20260904/134606980/1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G169"/>
+  <dimension ref="A1:G173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -5041,6 +5041,114 @@
         <v>2</v>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/05</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/05</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/05</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/05</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5052,7 +5160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:F130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -9191,6 +9299,38 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/05</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/05</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>초록우산 경기남부가정위탁지원센터, 위탁가정 힐링캠프 성료</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kyeonggi.com/article/20260905580092</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G173"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -5149,6 +5149,114 @@
         <v>1</v>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/06</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/06</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/06</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/06</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D177" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5160,7 +5268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F130"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -9331,6 +9439,70 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/06</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/06</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>장성군, 늘봄건강마을 우수 경로당 대상 "숲안애(愛) 힐링캠프" 성료</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=810143</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/06</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/06</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>장성군 충무2동 경로당 어르신 숲체원 힐링캠프</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>https://www.jnilbo.com/news/articleView.html?idxno=90000062677</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G177"/>
+  <dimension ref="A1:G181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -5257,6 +5257,114 @@
         <v>2</v>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D178" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D181" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G181" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5268,7 +5376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -9503,6 +9611,358 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>자영업자 아프거나 다쳐도 대출상환 '걱정 끝'…전남광주, 무료보험 9월부터</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bigkinds.or.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>전남광주시, 사고·질병 대비 '소상공인 상생보험' 9월 첫 시행</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>https://www.newspim.com/news/view/20260907000246</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>전남광주 소상공인 무료보험 첫 시행…대출금 최대 1천만원 상환</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bigkinds.or.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>광주특별시 '소상공인 무료 상생보험' 시행</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ajunews.com/view/20260907093632044</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>'소상공인 경영 안정 돕는다'...광주특별시, 9월부터 '소상공인 무료 상생보험' 시행</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>https://www.fnnews.com/news/202609070855011167</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>전남광주 소상공인, 9월부터 무료 상생보험 혜택 적용</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>https://www.namdonews.com/news/articleView.html?idxno=922463</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>‘개선 노력’에도 바뀌지 않는 현실… 때론 긍정하지 않는 것이 윤리다[김영민의 본다는 것은]</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/Opinion/article/all/20260906/134615436/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>연제구, 양성평등주간 운영 및 기념 행사 개최</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>https://www.busan.com/view/busan/view.php?code=2026090716010921318</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>"국가·국민 안전 최전선 헌신 감사" 강원랜드 제복 근무자 초청 캠프</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kado.net/news/articleView.html?idxno=2070928</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>강원랜드, 제복 영웅 가족 위한 2차 힐링캠프 성료</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kwnews.co.kr/article/20260905500110</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>남도일보</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>[지면 13면] 장성, 충무2동경로당숲안애힐링캠프</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>https://www.namdonews.com/pdf/php/check.php?category=&amp;y=2026&amp;m=09&amp;d=07&amp;page=13&amp;hosu=0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -5365,6 +5365,114 @@
         <v>4</v>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D182" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D183" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D184" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D185" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5376,7 +5484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -9963,6 +10071,294 @@
         </is>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>전남광주, 산하기관 11개로 통·폐합 추진</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.segye.com/newsView/20260907514300</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>소상공인이 살아야 지역경제가 산다…전남광주, ‘무료 상생보험’ 가동</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.viva100.com/article/20260907500204</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>“일하고도 못 받았다” 외국인노동자 임금체불 1548억…1년 새 43.6% 폭증</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sedaily.com/article/20088520?ref=kpf</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>작년 외국인노동자 임금체불액 1548억…전년대비 44% 급증</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>http://www.mk.co.kr/article/12147178</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>외국인 노동자 임금체불 109억원…올 상반기도 63억원</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>https://view.asiae.co.kr/article/2026090814364485777</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>"외국인노동자 임금 체불 1년새 44% 급증…작년 1548억원"</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>https://weekly.hankooki.com/news/articleView.html?idxno=7183098</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>외국인노동자 임금 1548억 떼여…제조·건설업 등에 피해 집중돼</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mt.co.kr/policy/2026/09/08/2026090809482543674</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>외국인 노동자 체불액 1500억 돌파…1년 새 43.6% 폭증</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>https://www.jnilbo.com/news/articleView.html?idxno=90000063379</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>장성군, 우수 경로당 어르신 초청 ‘숲안애 힐링캠프’ 운영</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>https://sports.donga.com/news/article/all/20260908/134626705/1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:G189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -5473,6 +5473,114 @@
         <v>1</v>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/09</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/09</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D187" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/09</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D188" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/09</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D189" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5484,7 +5592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F152"/>
+  <dimension ref="A1:F158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -10359,6 +10467,198 @@
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/09</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/09</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>거제시의회도 삼성·한화 조선소 설계인력 부산 확대에 "전면 재검토" 요구</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>https://www.idomin.com/news/articleView.html?idxno=2014485</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/09</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/09</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>금년 4회차 외국인노동자 신규 고용허가 신청 접수</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>http://www.pttimes.com/news/articleView.html?idxno=80039</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/09</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/09</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>문승호 경기도의원, 공공의료부터 정신건강까지 도민 보건안전망 전반 점검</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>https://go.seoul.co.kr/news/newsView.php?id=20260909500185</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/09</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/09</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>“금융인에서 문화예술 플랫폼 리더로”…100인의 힐링 공동체를 일군 윤정희 함성 인문학 힐링캠프 대표</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sportsseoul.com/news/read/1633922</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/09</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/09</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>부산시, 생명나눔 문화 확산·기증자 예우 강화…장기기증의 날 기념식</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>https://www.newspim.com/news/view/20260909000180</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/09</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/09</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>“한 사람이 최대 9명 살린다”…부산, 장기기증 문화 확산 나선다</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sedaily.com/article/20088709?ref=kpf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G189"/>
+  <dimension ref="A1:G193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -5581,6 +5581,114 @@
         <v>4</v>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/10</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/10</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/10</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D192" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/10</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5592,7 +5700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F158"/>
+  <dimension ref="A1:F161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -10659,6 +10767,102 @@
         </is>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/10</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/10</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>보은군노인·장애인복지관, 장애인 가족과 함께한 1박 2일 '여수 기차여행'</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ccdailynews.com/news/articleView.html?idxno=2439802</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/10</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/10</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>"칭찬이 힘이 됩니다"…양평군, '칭찬주인공' 선정 공무원 격려</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bigkinds.or.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/10</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/10</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>부산시, ‘장기기증의 날’ 기념식 개최… 생명나눔 문화 확산</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>http://www.metroseoul.co.kr/article/20260909500467</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G193"/>
+  <dimension ref="A1:G197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -5689,6 +5689,114 @@
         <v>3</v>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/11</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D194" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/11</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D195" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/11</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D196" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E196" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/11</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D197" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5700,7 +5808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F161"/>
+  <dimension ref="A1:F166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -10863,6 +10971,166 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/11</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/11</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>전남광주 노사민정, ‘전 생애 노동교육’ 활성화 논의</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>http://www.gwangnam.co.kr/article.php?aid=1789087496546812010</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/11</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/11</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>“퇴직 즉시 美 떠나야”…트럼프, 취업비자 60일 유예기간 없앤다</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/Inter/article/all/20260911/134649521/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/11</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/11</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>현대엔지니어링, 거제 최대 1963가구 ‘힐스테이트 거제시그니처’ 10월 분양</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/Economy/article/all/20260910/134645762/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/11</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/11</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>"감정노동 지친 복지 현장에 휴식을"…태백시, 사회복지사 힐링캠프</t>
+        </is>
+      </c>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bigkinds.or.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/11</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/11</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>영화 ‘오디세이’ 열풍에 호메로스를 다시 읽다</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sportsseoul.com/news/read/1634423</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G197"/>
+  <dimension ref="A1:G201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -5797,6 +5797,114 @@
         <v>2</v>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/12</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D198" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/12</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D199" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/12</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D200" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/12</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D201" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5808,7 +5916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F166"/>
+  <dimension ref="A1:F168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -11131,6 +11239,70 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/12</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/12</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>신미숙 경기도의원, 국비 받은 공모사업도 도비 없어 추진 차질 지적</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>https://go.seoul.co.kr/news/newsView.php?id=20260912500047</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/12</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/12</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>MBK 김병주 피의자 조사…홈플러스 수사 어디로 [PS]</t>
+        </is>
+      </c>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>https://sports.donga.com/news/article/all/20260912/134654697/1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
